--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N216_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N216_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.718806096962878</v>
+        <v>1.579305990756468</v>
       </c>
       <c r="D2" t="n">
-        <v>45.40099117860754</v>
+        <v>7.377661066523726</v>
       </c>
       <c r="E2" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F2" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80670940195215</v>
+        <v>5.656090277817225</v>
       </c>
       <c r="D3" t="n">
-        <v>55.12939324897382</v>
+        <v>8.958526402958245</v>
       </c>
       <c r="E3" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F3" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.66039164748064</v>
+        <v>7.094813642715605</v>
       </c>
       <c r="D4" t="n">
-        <v>47.36971758666616</v>
+        <v>7.69757910783325</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F4" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.74341266834389</v>
+        <v>2.233304558605882</v>
       </c>
       <c r="D5" t="n">
-        <v>10.97214851463592</v>
+        <v>1.782974133628338</v>
       </c>
       <c r="E5" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F5" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.83984794270446</v>
+        <v>3.386475290689475</v>
       </c>
       <c r="D6" t="n">
-        <v>24.68524521228802</v>
+        <v>4.011352346996802</v>
       </c>
       <c r="E6" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F6" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.7077143008209</v>
+        <v>3.365003573883397</v>
       </c>
       <c r="D7" t="n">
-        <v>23.40302742791979</v>
+        <v>3.802991957036966</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F7" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.38456322622019</v>
+        <v>2.499991524260781</v>
       </c>
       <c r="D8" t="n">
-        <v>10.207596299924</v>
+        <v>1.658734398737651</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F8" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.26406261504264</v>
+        <v>4.105410174944429</v>
       </c>
       <c r="D9" t="n">
-        <v>25.07561696481998</v>
+        <v>4.074787756783246</v>
       </c>
       <c r="E9" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F9" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.055194296063737</v>
+        <v>0.9839690731103573</v>
       </c>
       <c r="D10" t="n">
-        <v>8.180550428769042</v>
+        <v>1.329339444674969</v>
       </c>
       <c r="E10" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F10" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.604989002317954</v>
+        <v>1.560810712876668</v>
       </c>
       <c r="D11" t="n">
-        <v>6.300976154179337</v>
+        <v>1.023908625054142</v>
       </c>
       <c r="E11" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F11" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.49864604711702</v>
+        <v>5.768529982656516</v>
       </c>
       <c r="D12" t="n">
-        <v>37.54541723773429</v>
+        <v>6.101130301131823</v>
       </c>
       <c r="E12" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F12" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.87915451511302</v>
+        <v>4.042862608705867</v>
       </c>
       <c r="D13" t="n">
-        <v>21.31105671657747</v>
+        <v>3.463046716443839</v>
       </c>
       <c r="E13" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F13" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>70.43990790872837</v>
+        <v>11.44648503516836</v>
       </c>
       <c r="D14" t="n">
-        <v>49.6734840958657</v>
+        <v>8.071941165578176</v>
       </c>
       <c r="E14" t="n">
-        <v>16.87369946835086</v>
+        <v>2.741976163607015</v>
       </c>
       <c r="F14" t="n">
-        <v>16.47914169581906</v>
+        <v>2.677860525570598</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
